--- a/data/trans_orig/P1001-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1001-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2007</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39209</t>
+          <t>39135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43543</t>
+          <t>43848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46686</t>
+          <t>46502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75679</t>
+          <t>75045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>233801</t>
+          <t>233875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>254684</t>
+          <t>253993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>217295</t>
+          <t>216990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239585</t>
+          <t>239067</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>458169</t>
+          <t>458803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>487162</t>
+          <t>487346</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29387</t>
+          <t>30028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55242</t>
+          <t>54816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>60335</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93140</t>
+          <t>93561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>98527</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137630</t>
+          <t>139048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>437833</t>
+          <t>438259</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>463688</t>
+          <t>463047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>410809</t>
+          <t>410388</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>442152</t>
+          <t>443614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>859394</t>
+          <t>857976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>900534</t>
+          <t>898497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>17017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>29868</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302659</t>
+          <t>301829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315602</t>
+          <t>315168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314615</t>
+          <t>313059</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328332</t>
+          <t>328388</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622538</t>
+          <t>624390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641607</t>
+          <t>641944</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40963</t>
+          <t>39843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27702</t>
+          <t>26442</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51308</t>
+          <t>50436</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341148</t>
+          <t>341468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354178</t>
+          <t>354066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>330493</t>
+          <t>331613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>351835</t>
+          <t>351858</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>678819</t>
+          <t>679691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>702425</t>
+          <t>703685</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24965</t>
+          <t>24266</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>19679</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>182198</t>
+          <t>182320</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195343</t>
+          <t>195434</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182703</t>
+          <t>183402</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199406</t>
+          <t>199588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>372706</t>
+          <t>370700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>392046</t>
+          <t>391297</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20716</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24915</t>
+          <t>25032</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260844</t>
+          <t>262225</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269927</t>
+          <t>269933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257428</t>
+          <t>256948</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271910</t>
+          <t>270938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>524040</t>
+          <t>523923</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>539731</t>
+          <t>539826</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24745</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47220</t>
+          <t>47980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51068</t>
+          <t>53491</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84027</t>
+          <t>83488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83817</t>
+          <t>84836</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122836</t>
+          <t>121550</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>567807</t>
+          <t>567047</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>590282</t>
+          <t>590374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>554192</t>
+          <t>554731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>587151</t>
+          <t>584728</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1130410</t>
+          <t>1131696</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1169429</t>
+          <t>1168410</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47321</t>
+          <t>47180</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>76604</t>
+          <t>77524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59086</t>
+          <t>60741</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92523</t>
+          <t>94242</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>114909</t>
+          <t>116097</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161149</t>
+          <t>161818</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>667191</t>
+          <t>666271</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>696474</t>
+          <t>696615</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>690988</t>
+          <t>689269</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>724425</t>
+          <t>722770</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1366157</t>
+          <t>1365488</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1412397</t>
+          <t>1411209</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>172453</t>
+          <t>171962</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>225005</t>
+          <t>228714</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>283244</t>
+          <t>285475</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>354868</t>
+          <t>353205</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,47 +3527,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>516514</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>475327</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>557935</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>8,38%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>516514</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>472859</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>560462</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3051538</t>
+          <t>3047829</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3104090</t>
+          <t>3104581</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3024329</t>
+          <t>3025992</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3095953</t>
+          <t>3093722</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,47 +3640,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6007</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6139227</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6097806</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6180414</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>91,62%</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6007</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6139227</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6095279</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6182882</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2012</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41851</t>
+          <t>41254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48652</t>
+          <t>48729</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77436</t>
+          <t>76374</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75429</t>
+          <t>76416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>111204</t>
+          <t>112638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252887</t>
+          <t>253484</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274380</t>
+          <t>273974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>209809</t>
+          <t>210871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>238593</t>
+          <t>238516</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>470779</t>
+          <t>469345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>506554</t>
+          <t>505567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29007</t>
+          <t>28324</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56273</t>
+          <t>55310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62377</t>
+          <t>62880</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98897</t>
+          <t>97674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97988</t>
+          <t>100639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143055</t>
+          <t>143590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449254</t>
+          <t>450217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>476520</t>
+          <t>477203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>423813</t>
+          <t>425036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>460333</t>
+          <t>459830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>885182</t>
+          <t>884647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>930249</t>
+          <t>927598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27216</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26705</t>
+          <t>26289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50520</t>
+          <t>50486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41929</t>
+          <t>41326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71559</t>
+          <t>70753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296830</t>
+          <t>297136</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313429</t>
+          <t>314038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290500</t>
+          <t>290534</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>314315</t>
+          <t>314731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>593507</t>
+          <t>594313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623137</t>
+          <t>623740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31727</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66499</t>
+          <t>67414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98191</t>
+          <t>100241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86261</t>
+          <t>85567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123696</t>
+          <t>124153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342255</t>
+          <t>343776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361109</t>
+          <t>361762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>290760</t>
+          <t>288710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322452</t>
+          <t>321537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>639237</t>
+          <t>638780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>676672</t>
+          <t>677366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18067</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29061</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53129</t>
+          <t>52860</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38164</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65666</t>
+          <t>64026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194551</t>
+          <t>194360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207547</t>
+          <t>207367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166462</t>
+          <t>166731</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190530</t>
+          <t>190460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366543</t>
+          <t>368183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394045</t>
+          <t>394057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>13868</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>33110</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21552</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>43232</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>42703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67709</t>
+          <t>69411</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239875</t>
+          <t>239817</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257989</t>
+          <t>259059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235923</t>
+          <t>236799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258479</t>
+          <t>257551</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485249</t>
+          <t>483547</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>512402</t>
+          <t>510255</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23335</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49352</t>
+          <t>46791</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42339</t>
+          <t>41081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73203</t>
+          <t>71209</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70396</t>
+          <t>71194</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108508</t>
+          <t>109064</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>613436</t>
+          <t>615997</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>639453</t>
+          <t>640427</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>619705</t>
+          <t>621699</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>650569</t>
+          <t>651827</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1247188</t>
+          <t>1246632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1285300</t>
+          <t>1284502</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52581</t>
+          <t>51950</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>89162</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111566</t>
+          <t>111715</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155491</t>
+          <t>156397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175993</t>
+          <t>176028</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>233581</t>
+          <t>235362</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>688999</t>
+          <t>689106</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>725580</t>
+          <t>726211</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>668362</t>
+          <t>667456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>712287</t>
+          <t>712138</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1368433</t>
+          <t>1366652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1426021</t>
+          <t>1425986</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>213601</t>
+          <t>211723</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>277081</t>
+          <t>274717</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>480563</t>
+          <t>480889</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>566098</t>
+          <t>568669</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>709853</t>
+          <t>710869</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>815980</t>
+          <t>817586</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3147707</t>
+          <t>3150071</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3211187</t>
+          <t>3213065</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2990211</t>
+          <t>2987640</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3075746</t>
+          <t>3075420</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6165117</t>
+          <t>6163511</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6271244</t>
+          <t>6270228</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2016</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>35942</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62070</t>
+          <t>61625</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60408</t>
+          <t>60074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89210</t>
+          <t>90470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100714</t>
+          <t>103044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141965</t>
+          <t>141241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,25%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231691</t>
+          <t>232136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>258178</t>
+          <t>257819</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199493</t>
+          <t>198233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228295</t>
+          <t>228629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>440499</t>
+          <t>441223</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>481750</t>
+          <t>479420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,31%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>37920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64007</t>
+          <t>63879</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49269</t>
+          <t>48642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80362</t>
+          <t>79793</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>478958</t>
+          <t>478913</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494335</t>
+          <t>494721</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459077</t>
+          <t>459205</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486877</t>
+          <t>485164</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945297</t>
+          <t>945866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>976390</t>
+          <t>977017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28305</t>
+          <t>28763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37515</t>
+          <t>36185</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305134</t>
+          <t>305666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315764</t>
+          <t>315559</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308004</t>
+          <t>307546</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325140</t>
+          <t>324729</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617359</t>
+          <t>618689</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638039</t>
+          <t>638010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45688</t>
+          <t>45764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63458</t>
+          <t>64976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98561</t>
+          <t>97642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93465</t>
+          <t>94535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134237</t>
+          <t>136371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324276</t>
+          <t>324200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345853</t>
+          <t>346365</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288722</t>
+          <t>289641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323825</t>
+          <t>322307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>623010</t>
+          <t>620876</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>663782</t>
+          <t>662712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17021</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25794</t>
+          <t>26769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17871</t>
+          <t>17857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36926</t>
+          <t>39438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193978</t>
+          <t>194200</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206333</t>
+          <t>206299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192793</t>
+          <t>191818</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209106</t>
+          <t>208371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>392882</t>
+          <t>390370</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411937</t>
+          <t>411951</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11608</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29889</t>
+          <t>28655</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50813</t>
+          <t>53284</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43752</t>
+          <t>44131</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76246</t>
+          <t>74585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233234</t>
+          <t>234468</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251515</t>
+          <t>251673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222302</t>
+          <t>219831</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246635</t>
+          <t>245337</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>459992</t>
+          <t>461653</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>492486</t>
+          <t>492107</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>31344</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>58810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72449</t>
+          <t>71268</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>109507</t>
+          <t>107942</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111219</t>
+          <t>110681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159005</t>
+          <t>155345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>597363</t>
+          <t>597748</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>626255</t>
+          <t>625214</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>581787</t>
+          <t>583352</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>618845</t>
+          <t>620026</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1188847</t>
+          <t>1192507</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1236633</t>
+          <t>1237171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>21806</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>42576</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49649</t>
+          <t>51524</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81750</t>
+          <t>84339</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>80851</t>
+          <t>80192</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>120709</t>
+          <t>120904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>734743</t>
+          <t>736007</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>755982</t>
+          <t>756777</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>744417</t>
+          <t>741828</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>776518</t>
+          <t>774643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1484041</t>
+          <t>1483846</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1523899</t>
+          <t>1524558</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>181184</t>
+          <t>179888</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>236112</t>
+          <t>236610</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>393719</t>
+          <t>390919</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>471155</t>
+          <t>475836</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>592027</t>
+          <t>595029</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>686199</t>
+          <t>687165</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3158238</t>
+          <t>3157740</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3213166</t>
+          <t>3214462</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3073387</t>
+          <t>3068706</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3150823</t>
+          <t>3153623</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6252693</t>
+          <t>6251727</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6346865</t>
+          <t>6343863</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2023</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11509</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26927</t>
+          <t>27210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>296810</t>
+          <t>295579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307970</t>
+          <t>308012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272658</t>
+          <t>272773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283233</t>
+          <t>283177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>574150</t>
+          <t>573867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>589568</t>
+          <t>588939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27957</t>
+          <t>27187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55475</t>
+          <t>58071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44760</t>
+          <t>45821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70572</t>
+          <t>69572</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79339</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116884</t>
+          <t>115647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462915</t>
+          <t>460319</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>490433</t>
+          <t>491203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>444397</t>
+          <t>445397</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470209</t>
+          <t>469148</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>916475</t>
+          <t>917712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954020</t>
+          <t>954459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24478</t>
+          <t>24320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21217</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35889</t>
+          <t>35618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56802</t>
+          <t>56188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291572</t>
+          <t>291730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305695</t>
+          <t>305192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310135</t>
+          <t>310866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327351</t>
+          <t>326533</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>607816</t>
+          <t>608430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>628729</t>
+          <t>629000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27824</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24894</t>
+          <t>27214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60547</t>
+          <t>62246</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44831</t>
+          <t>44416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83411</t>
+          <t>82225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283526</t>
+          <t>281350</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300510</t>
+          <t>300094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>415171</t>
+          <t>413472</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>450824</t>
+          <t>448504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>703657</t>
+          <t>704843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>742237</t>
+          <t>742652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27137</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19706</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32667</t>
+          <t>32906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168703</t>
+          <t>168944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175869</t>
+          <t>175891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180896</t>
+          <t>181325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193184</t>
+          <t>193006</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354108</t>
+          <t>353869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367069</t>
+          <t>367333</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22715</t>
+          <t>22299</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>15971</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28482</t>
+          <t>28424</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>47585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246921</t>
+          <t>247337</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260029</t>
+          <t>259820</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228574</t>
+          <t>228632</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240941</t>
+          <t>241085</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479269</t>
+          <t>479107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>496888</t>
+          <t>498153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41467</t>
+          <t>41095</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76886</t>
+          <t>76524</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47229</t>
+          <t>47526</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138696</t>
+          <t>138093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96147</t>
+          <t>94151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188790</t>
+          <t>190111</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>547393</t>
+          <t>547755</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>582812</t>
+          <t>583184</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>709924</t>
+          <t>710527</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>801391</t>
+          <t>801094</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1284109</t>
+          <t>1282788</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1376752</t>
+          <t>1378748</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>18381</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61187</t>
+          <t>61059</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>98450</t>
+          <t>99945</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135232</t>
+          <t>133757</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96436</t>
+          <t>96040</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192393</t>
+          <t>194995</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>867533</t>
+          <t>867661</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>912709</t>
+          <t>910339</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>581969</t>
+          <t>583444</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>618751</t>
+          <t>617256</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1453528</t>
+          <t>1450926</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1549485</t>
+          <t>1549881</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153091</t>
+          <t>150804</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>230943</t>
+          <t>230107</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>325389</t>
+          <t>323034</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>436584</t>
+          <t>440327</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>516011</t>
+          <t>514146</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>654703</t>
+          <t>652784</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3227668</t>
+          <t>3228504</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3305520</t>
+          <t>3307807</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3223215</t>
+          <t>3219472</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3334410</t>
+          <t>3336765</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6463706</t>
+          <t>6465625</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6602398</t>
+          <t>6604263</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1001-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1001-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>19480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39135</t>
+          <t>39101</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43848</t>
+          <t>42808</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46502</t>
+          <t>43782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75045</t>
+          <t>74362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>233875</t>
+          <t>233909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>253993</t>
+          <t>253530</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216990</t>
+          <t>218030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239067</t>
+          <t>239811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>458803</t>
+          <t>459486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>487346</t>
+          <t>490066</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30028</t>
+          <t>29384</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54816</t>
+          <t>55417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60335</t>
+          <t>61587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93561</t>
+          <t>91850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98527</t>
+          <t>98843</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139048</t>
+          <t>139331</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>438259</t>
+          <t>437658</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>463047</t>
+          <t>463691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>410388</t>
+          <t>412099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>443614</t>
+          <t>442362</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>857976</t>
+          <t>857693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>898497</t>
+          <t>898181</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>21755</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29868</t>
+          <t>30069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301829</t>
+          <t>304364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315168</t>
+          <t>315924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313059</t>
+          <t>313657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328388</t>
+          <t>328266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624390</t>
+          <t>624189</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641944</t>
+          <t>641660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39843</t>
+          <t>40196</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26442</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50436</t>
+          <t>51376</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341468</t>
+          <t>341088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354066</t>
+          <t>353831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>331613</t>
+          <t>331260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>679691</t>
+          <t>678751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>703685</t>
+          <t>703009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20988</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>9041</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24266</t>
+          <t>24617</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>19599</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40276</t>
+          <t>39471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>182320</t>
+          <t>182901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195434</t>
+          <t>195625</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183402</t>
+          <t>183051</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199588</t>
+          <t>198627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370700</t>
+          <t>371505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>391297</t>
+          <t>391377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25032</t>
+          <t>25155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262225</t>
+          <t>261679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269933</t>
+          <t>269875</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256948</t>
+          <t>257172</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270938</t>
+          <t>271644</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>523923</t>
+          <t>523800</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>539826</t>
+          <t>539242</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24653</t>
+          <t>23854</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47980</t>
+          <t>46951</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53491</t>
+          <t>53654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83488</t>
+          <t>82284</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84836</t>
+          <t>83683</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121550</t>
+          <t>121957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>567047</t>
+          <t>568076</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>590374</t>
+          <t>591173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>554731</t>
+          <t>555935</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>584728</t>
+          <t>584565</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1131696</t>
+          <t>1131289</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1168410</t>
+          <t>1169563</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47180</t>
+          <t>47339</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77524</t>
+          <t>77227</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60741</t>
+          <t>60731</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94242</t>
+          <t>93088</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116097</t>
+          <t>113772</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161818</t>
+          <t>158199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>666271</t>
+          <t>666568</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>696615</t>
+          <t>696456</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>689269</t>
+          <t>690423</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>722770</t>
+          <t>722780</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1365488</t>
+          <t>1369107</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1411209</t>
+          <t>1413534</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>171962</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>228714</t>
+          <t>227118</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>285475</t>
+          <t>284255</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>353205</t>
+          <t>353412</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>475327</t>
+          <t>473518</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>557935</t>
+          <t>564186</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3047829</t>
+          <t>3049425</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3104581</t>
+          <t>3104622</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3025992</t>
+          <t>3025785</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3093722</t>
+          <t>3094942</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6097806</t>
+          <t>6091555</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6180414</t>
+          <t>6182223</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20764</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41254</t>
+          <t>43028</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48729</t>
+          <t>48242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76374</t>
+          <t>77562</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76416</t>
+          <t>75190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112638</t>
+          <t>113616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253484</t>
+          <t>251710</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>273974</t>
+          <t>272944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210871</t>
+          <t>209683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>238516</t>
+          <t>239003</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>469345</t>
+          <t>468367</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>505567</t>
+          <t>506793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28324</t>
+          <t>28723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55310</t>
+          <t>55565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62880</t>
+          <t>63793</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97674</t>
+          <t>96833</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100639</t>
+          <t>101214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143590</t>
+          <t>142748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450217</t>
+          <t>449962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>477203</t>
+          <t>476804</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>425036</t>
+          <t>425877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>459830</t>
+          <t>458917</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>884647</t>
+          <t>885489</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927598</t>
+          <t>927023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,16%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26910</t>
+          <t>26705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26289</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50486</t>
+          <t>50251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>40084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70753</t>
+          <t>68009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297136</t>
+          <t>297341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314038</t>
+          <t>314232</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>290534</t>
+          <t>290769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>314731</t>
+          <t>314239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>594313</t>
+          <t>597057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623740</t>
+          <t>624982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>13063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>31408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67414</t>
+          <t>68305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100241</t>
+          <t>100019</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85567</t>
+          <t>85821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124153</t>
+          <t>124072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343776</t>
+          <t>342574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361762</t>
+          <t>360919</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>288710</t>
+          <t>288932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321537</t>
+          <t>320646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>638780</t>
+          <t>638861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>677366</t>
+          <t>677112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,75%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29131</t>
+          <t>29248</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52860</t>
+          <t>53056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64026</t>
+          <t>65840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194360</t>
+          <t>193958</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207367</t>
+          <t>207369</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166731</t>
+          <t>166535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190460</t>
+          <t>190343</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368183</t>
+          <t>366369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394057</t>
+          <t>394058</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>14401</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33110</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22480</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43232</t>
+          <t>43255</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42703</t>
+          <t>40925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69411</t>
+          <t>68886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239817</t>
+          <t>238482</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259059</t>
+          <t>258526</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236799</t>
+          <t>236776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257551</t>
+          <t>257573</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>483547</t>
+          <t>484072</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510255</t>
+          <t>512033</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22361</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46791</t>
+          <t>47551</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41081</t>
+          <t>42377</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71209</t>
+          <t>72257</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71194</t>
+          <t>70722</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109064</t>
+          <t>108466</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>615997</t>
+          <t>615237</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>640427</t>
+          <t>640232</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>621699</t>
+          <t>620651</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>651827</t>
+          <t>650531</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1246632</t>
+          <t>1247230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1284502</t>
+          <t>1284974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51950</t>
+          <t>54196</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>89055</t>
+          <t>87199</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111715</t>
+          <t>111313</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>156397</t>
+          <t>154168</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176028</t>
+          <t>175086</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>235362</t>
+          <t>233685</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>689106</t>
+          <t>690962</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726211</t>
+          <t>723965</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>667456</t>
+          <t>669685</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>712138</t>
+          <t>712540</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1366652</t>
+          <t>1368329</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1425986</t>
+          <t>1426928</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>211723</t>
+          <t>214993</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>274717</t>
+          <t>280066</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>480889</t>
+          <t>483844</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>568669</t>
+          <t>565020</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>710869</t>
+          <t>711750</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>817586</t>
+          <t>820954</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3150071</t>
+          <t>3144722</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3213065</t>
+          <t>3209795</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2987640</t>
+          <t>2991289</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3075420</t>
+          <t>3072465</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6163511</t>
+          <t>6160143</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6270228</t>
+          <t>6269347</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35942</t>
+          <t>35995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>60824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60074</t>
+          <t>59294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90470</t>
+          <t>89924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>103044</t>
+          <t>104379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141241</t>
+          <t>143640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232136</t>
+          <t>232937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257819</t>
+          <t>257766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198233</t>
+          <t>198779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>228629</t>
+          <t>229409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>441223</t>
+          <t>438824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>479420</t>
+          <t>478085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,08%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23662</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37920</t>
+          <t>35916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63879</t>
+          <t>63743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48642</t>
+          <t>48825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79793</t>
+          <t>82260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>478913</t>
+          <t>478946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494721</t>
+          <t>494259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>459205</t>
+          <t>459341</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485164</t>
+          <t>487168</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945866</t>
+          <t>943399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>977017</t>
+          <t>976834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28763</t>
+          <t>28853</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36185</t>
+          <t>36903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305666</t>
+          <t>304847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315559</t>
+          <t>315576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307546</t>
+          <t>307456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324729</t>
+          <t>324826</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>618689</t>
+          <t>617971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>638010</t>
+          <t>638842</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23599</t>
+          <t>23793</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45764</t>
+          <t>45189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64976</t>
+          <t>65227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97642</t>
+          <t>98160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94535</t>
+          <t>93592</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136371</t>
+          <t>135073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324200</t>
+          <t>324775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>346365</t>
+          <t>346171</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>289641</t>
+          <t>289123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>322307</t>
+          <t>322056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>620876</t>
+          <t>622174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>662712</t>
+          <t>663655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,64%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17021</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26769</t>
+          <t>24403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39438</t>
+          <t>37818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194200</t>
+          <t>194537</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206299</t>
+          <t>206277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191818</t>
+          <t>194184</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208371</t>
+          <t>208733</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390370</t>
+          <t>391990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411951</t>
+          <t>412615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28655</t>
+          <t>29378</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27778</t>
+          <t>27333</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53284</t>
+          <t>51897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44131</t>
+          <t>44001</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74585</t>
+          <t>74756</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>234468</t>
+          <t>233745</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>251673</t>
+          <t>251170</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219831</t>
+          <t>221218</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245337</t>
+          <t>245782</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461653</t>
+          <t>461482</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>492107</t>
+          <t>492237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>30798</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58810</t>
+          <t>58943</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71268</t>
+          <t>70443</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107942</t>
+          <t>107832</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>110681</t>
+          <t>109810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155345</t>
+          <t>156134</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>597748</t>
+          <t>597615</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>625214</t>
+          <t>625760</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>583352</t>
+          <t>583462</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>620026</t>
+          <t>620851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1192507</t>
+          <t>1191718</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1237171</t>
+          <t>1238042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42576</t>
+          <t>44290</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51524</t>
+          <t>50624</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84339</t>
+          <t>85509</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>80192</t>
+          <t>81243</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>120904</t>
+          <t>120368</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>736007</t>
+          <t>734293</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>756777</t>
+          <t>756831</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>741828</t>
+          <t>740658</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>774643</t>
+          <t>775543</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1483846</t>
+          <t>1484382</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1524558</t>
+          <t>1523507</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>179888</t>
+          <t>178431</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>236610</t>
+          <t>235824</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>390919</t>
+          <t>388455</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>475836</t>
+          <t>477619</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>595029</t>
+          <t>589503</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>687165</t>
+          <t>686955</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3157740</t>
+          <t>3158526</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3214462</t>
+          <t>3215919</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3068706</t>
+          <t>3066923</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3153623</t>
+          <t>3156087</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6251727</t>
+          <t>6251937</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6343863</t>
+          <t>6349389</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15864</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>10910</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27210</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>311798</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295579</t>
+          <t>305825</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>308012</t>
+          <t>316122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>279156</t>
+          <t>305151</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272773</t>
+          <t>299391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283177</t>
+          <t>309286</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>582759</t>
+          <t>616949</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573867</t>
+          <t>609479</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588939</t>
+          <t>622776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39737</t>
+          <t>40363</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27187</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58071</t>
+          <t>57784</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56263</t>
+          <t>58942</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45821</t>
+          <t>46276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69572</t>
+          <t>72649</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>95999</t>
+          <t>99305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>81425</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115647</t>
+          <t>120199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>478653</t>
+          <t>490284</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460319</t>
+          <t>472863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491203</t>
+          <t>501572</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>458706</t>
+          <t>487552</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445397</t>
+          <t>473845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469148</t>
+          <t>500218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>937360</t>
+          <t>977836</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>917712</t>
+          <t>956942</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954459</t>
+          <t>995716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24320</t>
+          <t>26730</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>30702</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22035</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37702</t>
+          <t>39930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>45165</t>
+          <t>48080</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35618</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56188</t>
+          <t>60111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>299904</t>
+          <t>298616</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291730</t>
+          <t>289263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305192</t>
+          <t>304605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>319548</t>
+          <t>325118</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310866</t>
+          <t>315890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326533</t>
+          <t>333509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>619453</t>
+          <t>623733</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>608430</t>
+          <t>611702</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>629000</t>
+          <t>633258</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348568</t>
+          <t>355820</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348568</t>
+          <t>355820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348568</t>
+          <t>355820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664618</t>
+          <t>671813</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664618</t>
+          <t>671813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664618</t>
+          <t>671813</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>33042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43094</t>
+          <t>48628</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>37613</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62246</t>
+          <t>63747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61557</t>
+          <t>69607</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44416</t>
+          <t>54679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82225</t>
+          <t>88727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>292887</t>
+          <t>350964</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>281350</t>
+          <t>338901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300094</t>
+          <t>359339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>432624</t>
+          <t>373333</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>413472</t>
+          <t>358214</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>448504</t>
+          <t>384348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>725511</t>
+          <t>724298</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>704843</t>
+          <t>705178</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>742652</t>
+          <t>739226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311350</t>
+          <t>371943</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311350</t>
+          <t>371943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311350</t>
+          <t>371943</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787068</t>
+          <t>793905</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787068</t>
+          <t>793905</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787068</t>
+          <t>793905</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>20153</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26708</t>
+          <t>26695</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>25889</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>20068</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32906</t>
+          <t>33603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>173214</t>
+          <t>199929</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168944</t>
+          <t>195563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175891</t>
+          <t>202728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>187925</t>
+          <t>206461</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181325</t>
+          <t>199919</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>193006</t>
+          <t>211272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>361139</t>
+          <t>406389</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>353869</t>
+          <t>398675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367333</t>
+          <t>412210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208033</t>
+          <t>226614</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208033</t>
+          <t>226614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208033</t>
+          <t>226614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386775</t>
+          <t>432278</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386775</t>
+          <t>432278</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386775</t>
+          <t>432278</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,67 +12412,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15277</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22299</t>
+          <t>21995</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>21816</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>16192</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>29351</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>8,27%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>21772</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>15971</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>28424</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,22 +12482,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37049</t>
+          <t>36824</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47585</t>
+          <t>46193</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -12525,67 +12525,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>254359</t>
+          <t>255699</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247337</t>
+          <t>248712</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259820</t>
+          <t>261357</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>96,55%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>241934</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>234399</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>247558</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>91,73%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>235284</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>228632</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>241085</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>91,53%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,27 +12595,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>489643</t>
+          <t>497633</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>479107</t>
+          <t>488264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>498153</t>
+          <t>505511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>55664</t>
+          <t>60411</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41095</t>
+          <t>44697</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76524</t>
+          <t>81459</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>98356</t>
+          <t>118166</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47526</t>
+          <t>99248</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138093</t>
+          <t>138123</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>154020</t>
+          <t>178577</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94151</t>
+          <t>156581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>190111</t>
+          <t>206815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>568615</t>
+          <t>659276</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>547755</t>
+          <t>638228</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>583184</t>
+          <t>674990</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>750264</t>
+          <t>653200</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710527</t>
+          <t>633243</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>801094</t>
+          <t>672118</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1318879</t>
+          <t>1312476</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1282788</t>
+          <t>1284238</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1378748</t>
+          <t>1334472</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>89,5%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848620</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848620</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848620</t>
+          <t>771366</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472899</t>
+          <t>1491053</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472899</t>
+          <t>1491053</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472899</t>
+          <t>1491053</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>40337</t>
+          <t>46188</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61059</t>
+          <t>60926</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>115910</t>
+          <t>128691</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99945</t>
+          <t>111372</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>133757</t>
+          <t>147547</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>156247</t>
+          <t>174880</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96040</t>
+          <t>153973</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>194995</t>
+          <t>197787</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>888383</t>
+          <t>751884</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>867661</t>
+          <t>737146</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>910339</t>
+          <t>763488</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>601291</t>
+          <t>702048</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>583444</t>
+          <t>683192</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>617256</t>
+          <t>719367</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1489674</t>
+          <t>1453931</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1450926</t>
+          <t>1431024</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1549881</t>
+          <t>1474838</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717201</t>
+          <t>830739</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717201</t>
+          <t>830739</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717201</t>
+          <t>830739</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1645921</t>
+          <t>1628811</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1645921</t>
+          <t>1628811</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1645921</t>
+          <t>1628811</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>198990</t>
+          <t>213109</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>150804</t>
+          <t>185392</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>230107</t>
+          <t>243544</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>323034</t>
+          <t>404522</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>440327</t>
+          <t>472033</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>593991</t>
+          <t>651118</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>514146</t>
+          <t>605652</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>652784</t>
+          <t>698833</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>8,34%</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3259621</t>
+          <t>3318451</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3228504</t>
+          <t>3288016</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3307807</t>
+          <t>3346168</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3264798</t>
+          <t>3294797</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3219472</t>
+          <t>3260773</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3336765</t>
+          <t>3328284</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6524418</t>
+          <t>6613248</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6465625</t>
+          <t>6565533</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6604263</t>
+          <t>6658714</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>91,66%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3659799</t>
+          <t>3732806</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3659799</t>
+          <t>3732806</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3659799</t>
+          <t>3732806</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7118409</t>
+          <t>7264366</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7118409</t>
+          <t>7264366</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7118409</t>
+          <t>7264366</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
